--- a/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
@@ -990,6 +990,12 @@
   </x:si>
   <x:si>
     <x:t>PS空盘下降回零流程.StepID = 500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-04 08:34:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -8270,6 +8276,48 @@
         <x:v>191</x:v>
       </x:c>
     </x:row>
+    <x:row r="495" spans="1:4">
+      <x:c r="A495" s="1">
+        <x:v>45873.3576140046</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D495" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:4">
+      <x:c r="A496" s="1">
+        <x:v>45873.3576142245</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D496" s="2" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:4">
+      <x:c r="A497" s="1">
+        <x:v>45873.3577403125</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D497" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
@@ -993,6 +993,66 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-08-04 08:34:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 19:38:03]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 20:13:56]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 20:16:15]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 20:19:30]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 20:48:41]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 20:54:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 21:20:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-06 21:39:06]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-07 17:57:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-07 18:24:40]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
@@ -8318,6 +8378,426 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
+    <x:row r="498" spans="1:4">
+      <x:c r="A498" s="1">
+        <x:v>45875.8180989699</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D498" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:4">
+      <x:c r="A499" s="1">
+        <x:v>45875.8180991898</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D499" s="2" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:4">
+      <x:c r="A500" s="1">
+        <x:v>45875.8182309144</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D500" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:4">
+      <x:c r="A501" s="1">
+        <x:v>45875.8430175463</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D501" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:4">
+      <x:c r="A502" s="1">
+        <x:v>45875.8430177315</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D502" s="2" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:4">
+      <x:c r="A503" s="1">
+        <x:v>45875.8431454861</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D503" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:4">
+      <x:c r="A504" s="1">
+        <x:v>45875.8446208565</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D504" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:4">
+      <x:c r="A505" s="1">
+        <x:v>45875.8446210301</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D505" s="2" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:4">
+      <x:c r="A506" s="1">
+        <x:v>45875.8447437384</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D506" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:4">
+      <x:c r="A507" s="1">
+        <x:v>45875.8468838542</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D507" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:4">
+      <x:c r="A508" s="1">
+        <x:v>45875.8468840509</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D508" s="2" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:4">
+      <x:c r="A509" s="1">
+        <x:v>45875.8470152199</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D509" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:4">
+      <x:c r="A510" s="1">
+        <x:v>45875.8671523727</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D510" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:4">
+      <x:c r="A511" s="1">
+        <x:v>45875.8671525463</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D511" s="2" t="s">
+        <x:v>312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:4">
+      <x:c r="A512" s="1">
+        <x:v>45875.8674486458</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D512" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:4">
+      <x:c r="A513" s="1">
+        <x:v>45875.8714565278</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D513" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:4">
+      <x:c r="A514" s="1">
+        <x:v>45875.8714578935</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D514" s="2" t="s">
+        <x:v>313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:4">
+      <x:c r="A515" s="1">
+        <x:v>45875.8715858102</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D515" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:4">
+      <x:c r="A516" s="1">
+        <x:v>45875.8888988079</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D516" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:4">
+      <x:c r="A517" s="1">
+        <x:v>45875.8888989699</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D517" s="2" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:4">
+      <x:c r="A518" s="1">
+        <x:v>45875.8890251273</x:v>
+      </x:c>
+      <x:c r="B518" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C518" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D518" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:4">
+      <x:c r="A519" s="1">
+        <x:v>45875.9021558333</x:v>
+      </x:c>
+      <x:c r="B519" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C519" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D519" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:4">
+      <x:c r="A520" s="1">
+        <x:v>45875.9021560185</x:v>
+      </x:c>
+      <x:c r="B520" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C520" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D520" s="2" t="s">
+        <x:v>315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:4">
+      <x:c r="A521" s="1">
+        <x:v>45875.9022979051</x:v>
+      </x:c>
+      <x:c r="B521" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C521" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D521" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:4">
+      <x:c r="A522" s="1">
+        <x:v>45876.7479183796</x:v>
+      </x:c>
+      <x:c r="B522" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D522" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:4">
+      <x:c r="A523" s="1">
+        <x:v>45876.7479186111</x:v>
+      </x:c>
+      <x:c r="B523" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C523" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D523" s="2" t="s">
+        <x:v>316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:4">
+      <x:c r="A524" s="1">
+        <x:v>45876.7480474884</x:v>
+      </x:c>
+      <x:c r="B524" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C524" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D524" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:4">
+      <x:c r="A525" s="1">
+        <x:v>45876.7671342361</x:v>
+      </x:c>
+      <x:c r="B525" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C525" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D525" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:4">
+      <x:c r="A526" s="1">
+        <x:v>45876.7671343981</x:v>
+      </x:c>
+      <x:c r="B526" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C526" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D526" s="2" t="s">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:4">
+      <x:c r="A527" s="1">
+        <x:v>45876.7672683218</x:v>
+      </x:c>
+      <x:c r="B527" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C527" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D527" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
@@ -1053,6 +1053,234 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-08-07 18:24:40]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-07 19:40:44]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 10:10:39]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400420,[Msg]归零失败!未初始化;未初始化;未初始化;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>归零失败</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 15:06:16]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 16:14:55]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 17:17:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 17:20:41]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 17:31:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 20:13:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-09 20:18:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-11 21:20:41]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[测试超时时间]:600-&gt;10:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@START_TEST 00 11111111+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-11 21:29:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:16:55]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:22:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:34:51]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:36:16]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:39:48]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 09:41:01]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 11:22:59]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 11:26:26]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 11:30:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 11:33:47]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 11:35:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 14:00:47]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:10:26]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:12:27]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:14:06]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:15:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:23:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:25:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:27:38]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:28:40]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:29:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:30:54]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:32:16]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:40:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-12 16:52:58]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
@@ -8798,6 +9026,1560 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
+    <x:row r="528" spans="1:4">
+      <x:c r="A528" s="1">
+        <x:v>45876.819955162</x:v>
+      </x:c>
+      <x:c r="B528" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C528" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D528" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:4">
+      <x:c r="A529" s="1">
+        <x:v>45876.8199553588</x:v>
+      </x:c>
+      <x:c r="B529" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C529" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D529" s="2" t="s">
+        <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:4">
+      <x:c r="A530" s="1">
+        <x:v>45878.424064919</x:v>
+      </x:c>
+      <x:c r="B530" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C530" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D530" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:4">
+      <x:c r="A531" s="1">
+        <x:v>45878.4240650926</x:v>
+      </x:c>
+      <x:c r="B531" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C531" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D531" s="2" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:4">
+      <x:c r="A532" s="1">
+        <x:v>45878.4243504398</x:v>
+      </x:c>
+      <x:c r="B532" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C532" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D532" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:4">
+      <x:c r="A533" s="1">
+        <x:v>45878.4243504514</x:v>
+      </x:c>
+      <x:c r="B533" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C533" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D533" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:4">
+      <x:c r="A534" s="1">
+        <x:v>45878.629360706</x:v>
+      </x:c>
+      <x:c r="B534" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C534" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D534" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:4">
+      <x:c r="A535" s="1">
+        <x:v>45878.6293608796</x:v>
+      </x:c>
+      <x:c r="B535" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C535" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D535" s="2" t="s">
+        <x:v>322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:4">
+      <x:c r="A536" s="1">
+        <x:v>45878.6294915972</x:v>
+      </x:c>
+      <x:c r="B536" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C536" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D536" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:4">
+      <x:c r="A537" s="1">
+        <x:v>45878.677034537</x:v>
+      </x:c>
+      <x:c r="B537" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C537" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D537" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:4">
+      <x:c r="A538" s="1">
+        <x:v>45878.6770353472</x:v>
+      </x:c>
+      <x:c r="B538" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C538" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D538" s="2" t="s">
+        <x:v>323</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:4">
+      <x:c r="A539" s="1">
+        <x:v>45878.6771671065</x:v>
+      </x:c>
+      <x:c r="B539" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C539" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D539" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:4">
+      <x:c r="A540" s="1">
+        <x:v>45878.720806331</x:v>
+      </x:c>
+      <x:c r="B540" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C540" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D540" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:4">
+      <x:c r="A541" s="1">
+        <x:v>45878.7208064931</x:v>
+      </x:c>
+      <x:c r="B541" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C541" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D541" s="2" t="s">
+        <x:v>324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:4">
+      <x:c r="A542" s="1">
+        <x:v>45878.7209322569</x:v>
+      </x:c>
+      <x:c r="B542" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C542" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D542" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:4">
+      <x:c r="A543" s="1">
+        <x:v>45878.722704213</x:v>
+      </x:c>
+      <x:c r="B543" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C543" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D543" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:4">
+      <x:c r="A544" s="1">
+        <x:v>45878.7227043866</x:v>
+      </x:c>
+      <x:c r="B544" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C544" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D544" s="2" t="s">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:4">
+      <x:c r="A545" s="1">
+        <x:v>45878.7228356134</x:v>
+      </x:c>
+      <x:c r="B545" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C545" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D545" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:4">
+      <x:c r="A546" s="1">
+        <x:v>45878.730081713</x:v>
+      </x:c>
+      <x:c r="B546" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C546" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D546" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:4">
+      <x:c r="A547" s="1">
+        <x:v>45878.7300818866</x:v>
+      </x:c>
+      <x:c r="B547" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C547" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D547" s="2" t="s">
+        <x:v>326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:4">
+      <x:c r="A548" s="1">
+        <x:v>45878.7303897917</x:v>
+      </x:c>
+      <x:c r="B548" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C548" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D548" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:4">
+      <x:c r="A549" s="1">
+        <x:v>45878.842768912</x:v>
+      </x:c>
+      <x:c r="B549" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C549" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D549" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:4">
+      <x:c r="A550" s="1">
+        <x:v>45878.8427692477</x:v>
+      </x:c>
+      <x:c r="B550" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C550" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D550" s="2" t="s">
+        <x:v>327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:4">
+      <x:c r="A551" s="1">
+        <x:v>45878.8462629514</x:v>
+      </x:c>
+      <x:c r="B551" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C551" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D551" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:4">
+      <x:c r="A552" s="1">
+        <x:v>45878.8462631366</x:v>
+      </x:c>
+      <x:c r="B552" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C552" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D552" s="2" t="s">
+        <x:v>328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:4">
+      <x:c r="A553" s="1">
+        <x:v>45880.889372581</x:v>
+      </x:c>
+      <x:c r="B553" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C553" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D553" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:4">
+      <x:c r="A554" s="1">
+        <x:v>45880.8893727662</x:v>
+      </x:c>
+      <x:c r="B554" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C554" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D554" s="2" t="s">
+        <x:v>329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:4">
+      <x:c r="A555" s="1">
+        <x:v>45880.889500162</x:v>
+      </x:c>
+      <x:c r="B555" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C555" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D555" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:4">
+      <x:c r="A556" s="1">
+        <x:v>45880.8895513657</x:v>
+      </x:c>
+      <x:c r="B556" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C556" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D556" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:4">
+      <x:c r="A557" s="1">
+        <x:v>45880.8903804745</x:v>
+      </x:c>
+      <x:c r="B557" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C557" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D557" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:4">
+      <x:c r="A558" s="1">
+        <x:v>45880.8904270718</x:v>
+      </x:c>
+      <x:c r="B558" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C558" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D558" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:4">
+      <x:c r="A559" s="1">
+        <x:v>45880.8922187037</x:v>
+      </x:c>
+      <x:c r="B559" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C559" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D559" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:4">
+      <x:c r="A560" s="1">
+        <x:v>45880.8953839699</x:v>
+      </x:c>
+      <x:c r="B560" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C560" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D560" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:4">
+      <x:c r="A561" s="1">
+        <x:v>45880.8953841551</x:v>
+      </x:c>
+      <x:c r="B561" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C561" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D561" s="2" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:4">
+      <x:c r="A562" s="1">
+        <x:v>45880.8955201389</x:v>
+      </x:c>
+      <x:c r="B562" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C562" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D562" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:4">
+      <x:c r="A563" s="1">
+        <x:v>45881.3867492361</x:v>
+      </x:c>
+      <x:c r="B563" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C563" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D563" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:4">
+      <x:c r="A564" s="1">
+        <x:v>45881.3867494676</x:v>
+      </x:c>
+      <x:c r="B564" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C564" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D564" s="2" t="s">
+        <x:v>333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:4">
+      <x:c r="A565" s="1">
+        <x:v>45881.3868807292</x:v>
+      </x:c>
+      <x:c r="B565" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C565" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D565" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:4">
+      <x:c r="A566" s="1">
+        <x:v>45881.390686169</x:v>
+      </x:c>
+      <x:c r="B566" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C566" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D566" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:4">
+      <x:c r="A567" s="1">
+        <x:v>45881.3906864236</x:v>
+      </x:c>
+      <x:c r="B567" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C567" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D567" s="2" t="s">
+        <x:v>334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:4">
+      <x:c r="A568" s="1">
+        <x:v>45881.3908163889</x:v>
+      </x:c>
+      <x:c r="B568" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C568" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D568" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:4">
+      <x:c r="A569" s="1">
+        <x:v>45881.3992069792</x:v>
+      </x:c>
+      <x:c r="B569" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C569" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D569" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:4">
+      <x:c r="A570" s="1">
+        <x:v>45881.3992071528</x:v>
+      </x:c>
+      <x:c r="B570" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C570" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D570" s="2" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:4">
+      <x:c r="A571" s="1">
+        <x:v>45881.3993383102</x:v>
+      </x:c>
+      <x:c r="B571" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C571" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D571" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:4">
+      <x:c r="A572" s="1">
+        <x:v>45881.4001846991</x:v>
+      </x:c>
+      <x:c r="B572" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C572" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D572" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:4">
+      <x:c r="A573" s="1">
+        <x:v>45881.4001854051</x:v>
+      </x:c>
+      <x:c r="B573" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C573" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D573" s="2" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:4">
+      <x:c r="A574" s="1">
+        <x:v>45881.4003208102</x:v>
+      </x:c>
+      <x:c r="B574" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C574" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D574" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:4">
+      <x:c r="A575" s="1">
+        <x:v>45881.4026388079</x:v>
+      </x:c>
+      <x:c r="B575" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C575" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D575" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:4">
+      <x:c r="A576" s="1">
+        <x:v>45881.4026389931</x:v>
+      </x:c>
+      <x:c r="B576" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C576" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D576" s="2" t="s">
+        <x:v>337</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:4">
+      <x:c r="A577" s="1">
+        <x:v>45881.4027640857</x:v>
+      </x:c>
+      <x:c r="B577" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C577" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D577" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:4">
+      <x:c r="A578" s="1">
+        <x:v>45881.4034934491</x:v>
+      </x:c>
+      <x:c r="B578" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C578" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D578" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:4">
+      <x:c r="A579" s="1">
+        <x:v>45881.4034936227</x:v>
+      </x:c>
+      <x:c r="B579" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C579" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D579" s="2" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:4">
+      <x:c r="A580" s="1">
+        <x:v>45881.4036189815</x:v>
+      </x:c>
+      <x:c r="B580" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C580" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D580" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:4">
+      <x:c r="A581" s="1">
+        <x:v>45881.4742966088</x:v>
+      </x:c>
+      <x:c r="B581" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C581" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D581" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:4">
+      <x:c r="A582" s="1">
+        <x:v>45881.4742969213</x:v>
+      </x:c>
+      <x:c r="B582" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C582" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D582" s="2" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:4">
+      <x:c r="A583" s="1">
+        <x:v>45881.4744233333</x:v>
+      </x:c>
+      <x:c r="B583" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C583" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D583" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:4">
+      <x:c r="A584" s="1">
+        <x:v>45881.4766957986</x:v>
+      </x:c>
+      <x:c r="B584" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C584" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D584" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:4">
+      <x:c r="A585" s="1">
+        <x:v>45881.4766959838</x:v>
+      </x:c>
+      <x:c r="B585" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C585" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D585" s="2" t="s">
+        <x:v>340</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:4">
+      <x:c r="A586" s="1">
+        <x:v>45881.4768151157</x:v>
+      </x:c>
+      <x:c r="B586" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C586" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D586" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:4">
+      <x:c r="A587" s="1">
+        <x:v>45881.4796693056</x:v>
+      </x:c>
+      <x:c r="B587" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C587" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D587" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:4">
+      <x:c r="A588" s="1">
+        <x:v>45881.4796694676</x:v>
+      </x:c>
+      <x:c r="B588" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C588" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D588" s="2" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:4">
+      <x:c r="A589" s="1">
+        <x:v>45881.4798008681</x:v>
+      </x:c>
+      <x:c r="B589" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C589" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D589" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:4">
+      <x:c r="A590" s="1">
+        <x:v>45881.4818020023</x:v>
+      </x:c>
+      <x:c r="B590" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C590" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D590" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:4">
+      <x:c r="A591" s="1">
+        <x:v>45881.4818021759</x:v>
+      </x:c>
+      <x:c r="B591" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C591" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D591" s="2" t="s">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:4">
+      <x:c r="A592" s="1">
+        <x:v>45881.4819332639</x:v>
+      </x:c>
+      <x:c r="B592" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C592" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D592" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:4">
+      <x:c r="A593" s="1">
+        <x:v>45881.4828907407</x:v>
+      </x:c>
+      <x:c r="B593" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C593" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D593" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:4">
+      <x:c r="A594" s="1">
+        <x:v>45881.4828909259</x:v>
+      </x:c>
+      <x:c r="B594" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C594" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D594" s="2" t="s">
+        <x:v>343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:4">
+      <x:c r="A595" s="1">
+        <x:v>45881.4830195833</x:v>
+      </x:c>
+      <x:c r="B595" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C595" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D595" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:4">
+      <x:c r="A596" s="1">
+        <x:v>45881.5838800926</x:v>
+      </x:c>
+      <x:c r="B596" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C596" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D596" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:4">
+      <x:c r="A597" s="1">
+        <x:v>45881.5838802662</x:v>
+      </x:c>
+      <x:c r="B597" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C597" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D597" s="2" t="s">
+        <x:v>344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:4">
+      <x:c r="A598" s="1">
+        <x:v>45881.5839709838</x:v>
+      </x:c>
+      <x:c r="B598" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C598" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D598" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:4">
+      <x:c r="A599" s="1">
+        <x:v>45881.5840048958</x:v>
+      </x:c>
+      <x:c r="B599" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C599" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D599" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:4">
+      <x:c r="A600" s="1">
+        <x:v>45881.6739166319</x:v>
+      </x:c>
+      <x:c r="B600" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C600" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D600" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:4">
+      <x:c r="A601" s="1">
+        <x:v>45881.6739168056</x:v>
+      </x:c>
+      <x:c r="B601" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C601" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D601" s="2" t="s">
+        <x:v>345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:4">
+      <x:c r="A602" s="1">
+        <x:v>45881.6740434838</x:v>
+      </x:c>
+      <x:c r="B602" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C602" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D602" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:4">
+      <x:c r="A603" s="1">
+        <x:v>45881.6753123958</x:v>
+      </x:c>
+      <x:c r="B603" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C603" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D603" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:4">
+      <x:c r="A604" s="1">
+        <x:v>45881.6753128704</x:v>
+      </x:c>
+      <x:c r="B604" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C604" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D604" s="2" t="s">
+        <x:v>346</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:4">
+      <x:c r="A605" s="1">
+        <x:v>45881.6754379745</x:v>
+      </x:c>
+      <x:c r="B605" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C605" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D605" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:4">
+      <x:c r="A606" s="1">
+        <x:v>45881.6764590625</x:v>
+      </x:c>
+      <x:c r="B606" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C606" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D606" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:4">
+      <x:c r="A607" s="1">
+        <x:v>45881.6764593981</x:v>
+      </x:c>
+      <x:c r="B607" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C607" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D607" s="2" t="s">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:4">
+      <x:c r="A608" s="1">
+        <x:v>45881.6765803935</x:v>
+      </x:c>
+      <x:c r="B608" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C608" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D608" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:4">
+      <x:c r="A609" s="1">
+        <x:v>45881.6777055787</x:v>
+      </x:c>
+      <x:c r="B609" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C609" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D609" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:4">
+      <x:c r="A610" s="1">
+        <x:v>45881.6777059259</x:v>
+      </x:c>
+      <x:c r="B610" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C610" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D610" s="2" t="s">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:4">
+      <x:c r="A611" s="1">
+        <x:v>45881.6778235764</x:v>
+      </x:c>
+      <x:c r="B611" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C611" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D611" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:4">
+      <x:c r="A612" s="1">
+        <x:v>45881.6828661574</x:v>
+      </x:c>
+      <x:c r="B612" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C612" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D612" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:4">
+      <x:c r="A613" s="1">
+        <x:v>45881.682866331</x:v>
+      </x:c>
+      <x:c r="B613" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C613" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D613" s="2" t="s">
+        <x:v>349</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:4">
+      <x:c r="A614" s="1">
+        <x:v>45881.6829940046</x:v>
+      </x:c>
+      <x:c r="B614" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C614" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D614" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:4">
+      <x:c r="A615" s="1">
+        <x:v>45881.6843874074</x:v>
+      </x:c>
+      <x:c r="B615" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C615" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D615" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:4">
+      <x:c r="A616" s="1">
+        <x:v>45881.684387581</x:v>
+      </x:c>
+      <x:c r="B616" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C616" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D616" s="2" t="s">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:4">
+      <x:c r="A617" s="1">
+        <x:v>45881.6845103704</x:v>
+      </x:c>
+      <x:c r="B617" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C617" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D617" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:4">
+      <x:c r="A618" s="1">
+        <x:v>45881.6858633102</x:v>
+      </x:c>
+      <x:c r="B618" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C618" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D618" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:4">
+      <x:c r="A619" s="1">
+        <x:v>45881.6858634838</x:v>
+      </x:c>
+      <x:c r="B619" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C619" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D619" s="2" t="s">
+        <x:v>351</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:4">
+      <x:c r="A620" s="1">
+        <x:v>45881.6859867824</x:v>
+      </x:c>
+      <x:c r="B620" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C620" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D620" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:4">
+      <x:c r="A621" s="1">
+        <x:v>45881.6865743403</x:v>
+      </x:c>
+      <x:c r="B621" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C621" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D621" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:4">
+      <x:c r="A622" s="1">
+        <x:v>45881.6865745255</x:v>
+      </x:c>
+      <x:c r="B622" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C622" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D622" s="2" t="s">
+        <x:v>352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:4">
+      <x:c r="A623" s="1">
+        <x:v>45881.6867039352</x:v>
+      </x:c>
+      <x:c r="B623" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C623" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D623" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:4">
+      <x:c r="A624" s="1">
+        <x:v>45881.6873120023</x:v>
+      </x:c>
+      <x:c r="B624" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C624" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D624" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:4">
+      <x:c r="A625" s="1">
+        <x:v>45881.6873121759</x:v>
+      </x:c>
+      <x:c r="B625" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C625" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D625" s="2" t="s">
+        <x:v>353</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" spans="1:4">
+      <x:c r="A626" s="1">
+        <x:v>45881.6874377778</x:v>
+      </x:c>
+      <x:c r="B626" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C626" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D626" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" spans="1:4">
+      <x:c r="A627" s="1">
+        <x:v>45881.6881272106</x:v>
+      </x:c>
+      <x:c r="B627" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C627" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D627" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" spans="1:4">
+      <x:c r="A628" s="1">
+        <x:v>45881.6881275347</x:v>
+      </x:c>
+      <x:c r="B628" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C628" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D628" s="2" t="s">
+        <x:v>354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" spans="1:4">
+      <x:c r="A629" s="1">
+        <x:v>45881.6882527662</x:v>
+      </x:c>
+      <x:c r="B629" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C629" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D629" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" spans="1:4">
+      <x:c r="A630" s="1">
+        <x:v>45881.6890781134</x:v>
+      </x:c>
+      <x:c r="B630" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C630" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D630" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" spans="1:4">
+      <x:c r="A631" s="1">
+        <x:v>45881.6890784375</x:v>
+      </x:c>
+      <x:c r="B631" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C631" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D631" s="2" t="s">
+        <x:v>355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" spans="1:4">
+      <x:c r="A632" s="1">
+        <x:v>45881.6892016551</x:v>
+      </x:c>
+      <x:c r="B632" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C632" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D632" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" spans="1:4">
+      <x:c r="A633" s="1">
+        <x:v>45881.6950477315</x:v>
+      </x:c>
+      <x:c r="B633" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C633" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D633" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" spans="1:4">
+      <x:c r="A634" s="1">
+        <x:v>45881.6950479051</x:v>
+      </x:c>
+      <x:c r="B634" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C634" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D634" s="2" t="s">
+        <x:v>356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" spans="1:4">
+      <x:c r="A635" s="1">
+        <x:v>45881.6951698495</x:v>
+      </x:c>
+      <x:c r="B635" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C635" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D635" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" spans="1:4">
+      <x:c r="A636" s="1">
+        <x:v>45881.7034543287</x:v>
+      </x:c>
+      <x:c r="B636" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C636" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D636" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" spans="1:4">
+      <x:c r="A637" s="1">
+        <x:v>45881.7034545023</x:v>
+      </x:c>
+      <x:c r="B637" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C637" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D637" s="2" t="s">
+        <x:v>357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" spans="1:4">
+      <x:c r="A638" s="1">
+        <x:v>45881.7035796991</x:v>
+      </x:c>
+      <x:c r="B638" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C638" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D638" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
@@ -1281,6 +1281,45 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-08-12 16:52:58]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-13 10:51:18]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-13 11:30:47]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400449,[Msg]读取Site1-Site8探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400450,[Msg]读取Site9-Site16探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400451,[Msg]读取加热盘探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-13 15:19:50]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-13 15:48:14]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-08-13 19:11:24]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
@@ -10580,6 +10619,328 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
+    <x:row r="639" spans="1:4">
+      <x:c r="A639" s="1">
+        <x:v>45882.4522963889</x:v>
+      </x:c>
+      <x:c r="B639" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C639" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D639" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" spans="1:4">
+      <x:c r="A640" s="1">
+        <x:v>45882.4522965856</x:v>
+      </x:c>
+      <x:c r="B640" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C640" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D640" s="2" t="s">
+        <x:v>358</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" spans="1:4">
+      <x:c r="A641" s="1">
+        <x:v>45882.452427037</x:v>
+      </x:c>
+      <x:c r="B641" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C641" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D641" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" spans="1:4">
+      <x:c r="A642" s="1">
+        <x:v>45882.4797166551</x:v>
+      </x:c>
+      <x:c r="B642" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C642" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D642" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" spans="1:4">
+      <x:c r="A643" s="1">
+        <x:v>45882.4797168171</x:v>
+      </x:c>
+      <x:c r="B643" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C643" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D643" s="2" t="s">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" spans="1:4">
+      <x:c r="A644" s="1">
+        <x:v>45882.4802784838</x:v>
+      </x:c>
+      <x:c r="B644" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C644" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D644" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" spans="1:4">
+      <x:c r="A645" s="1">
+        <x:v>45882.4803230787</x:v>
+      </x:c>
+      <x:c r="B645" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C645" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D645" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" spans="1:4">
+      <x:c r="A646" s="1">
+        <x:v>45882.4803635995</x:v>
+      </x:c>
+      <x:c r="B646" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C646" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D646" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" spans="1:4">
+      <x:c r="A647" s="1">
+        <x:v>45882.6387825694</x:v>
+      </x:c>
+      <x:c r="B647" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C647" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D647" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" spans="1:4">
+      <x:c r="A648" s="1">
+        <x:v>45882.6387827546</x:v>
+      </x:c>
+      <x:c r="B648" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C648" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D648" s="2" t="s">
+        <x:v>363</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" spans="1:4">
+      <x:c r="A649" s="1">
+        <x:v>45882.6391418171</x:v>
+      </x:c>
+      <x:c r="B649" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C649" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D649" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" spans="1:4">
+      <x:c r="A650" s="1">
+        <x:v>45882.639141875</x:v>
+      </x:c>
+      <x:c r="B650" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C650" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D650" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" spans="1:4">
+      <x:c r="A651" s="1">
+        <x:v>45882.6391418866</x:v>
+      </x:c>
+      <x:c r="B651" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C651" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D651" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" spans="1:4">
+      <x:c r="A652" s="1">
+        <x:v>45882.65850375</x:v>
+      </x:c>
+      <x:c r="B652" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C652" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D652" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" spans="1:4">
+      <x:c r="A653" s="1">
+        <x:v>45882.6585039236</x:v>
+      </x:c>
+      <x:c r="B653" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C653" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D653" s="2" t="s">
+        <x:v>364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" spans="1:4">
+      <x:c r="A654" s="1">
+        <x:v>45882.6588697685</x:v>
+      </x:c>
+      <x:c r="B654" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C654" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D654" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" spans="1:4">
+      <x:c r="A655" s="1">
+        <x:v>45882.6588697917</x:v>
+      </x:c>
+      <x:c r="B655" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C655" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D655" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" spans="1:4">
+      <x:c r="A656" s="1">
+        <x:v>45882.6588698032</x:v>
+      </x:c>
+      <x:c r="B656" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C656" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D656" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" spans="1:4">
+      <x:c r="A657" s="1">
+        <x:v>45882.7995890856</x:v>
+      </x:c>
+      <x:c r="B657" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C657" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D657" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" spans="1:4">
+      <x:c r="A658" s="1">
+        <x:v>45882.7995896181</x:v>
+      </x:c>
+      <x:c r="B658" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C658" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D658" s="2" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" spans="1:4">
+      <x:c r="A659" s="1">
+        <x:v>45882.7997207986</x:v>
+      </x:c>
+      <x:c r="B659" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C659" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D659" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" spans="1:4">
+      <x:c r="A660" s="1">
+        <x:v>45882.7998367824</x:v>
+      </x:c>
+      <x:c r="B660" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C660" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D660" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" spans="1:4">
+      <x:c r="A661" s="1">
+        <x:v>45882.7999528241</x:v>
+      </x:c>
+      <x:c r="B661" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C661" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D661" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-220610.xlsx
@@ -11,1320 +11,6 @@
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
 </x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>日志时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志等级</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志内容</x:t>
-  </x:si>
-  <x:si>
-    <x:t>debug</x:t>
-  </x:si>
-  <x:si>
-    <x:t>run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTN_Open(5,1):(-6)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-01 22:06:08]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error)
-   在 H5509_V2.Motion.InitCard()</x:t>
-  </x:si>
-  <x:si>
-    <x:t>加载已有文件失败: D:\GitHub\H5509_V2\bin\Debug\Logs\202508\Log_20250801-090757.xlsx
-压缩部分具有不一致的数据长度。</x:t>
-  </x:si>
-  <x:si>
-    <x:t>创建新文件: D:\GitHub\H5509_V2\bin\Debug\Logs\202508\Log_20250801-220610.xlsx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400448,[Msg]温控器连接失败!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>档案名称-[默认]-加热盘名称-[默认]-[达温后延时]20-&gt;10:更新成功</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 09:35:54]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 09:51:00]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>密码错误！</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 10:42:54]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:07:39]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:15:10]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:27:42]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>档案名称:[8X19_UFS_OnLine]:加热盘名称:默认-&gt;6x12_eMMC:更新成功</x:t>
-  </x:si>
-  <x:si>
-    <x:t>档案名称:[8X19_UFS_OnLine]:温度模式:常温-&gt;高温:更新成功</x:t>
-  </x:si>
-  <x:si>
-    <x:t>档案名称:[8X19_UFS_OnLine]:加热盘名称:6x12_eMMC-&gt;6x12_UFS:更新成功</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:29:58]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:32:54]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:34:11]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:43:23]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:47:29]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:51:56]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 11:55:22]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 13:47:05]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>设备状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>温控达温 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>初次达温 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H5509归零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H5509正在归零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H5509初始化 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H5509正在初始化 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>结批标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>正在结批 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>结批完成 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>强制结批标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>定点停止标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>后方定点停止允许 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>前方定点停止允许 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>开舱门上顶标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load舱门上顶标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty舱门上顶标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1舱门上顶标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2舱门上顶标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load舱门开启标记 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty舱门开启标记 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1舱门开启标记 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2舱门开启标记 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty下降回零开关 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load下降回零开关 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1下降回零开关 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2下降回零开关 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty正在下降回零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load正在下降回零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1正在下降回零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2正在下降回零 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty舱门正在上顶 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load舱门正在上顶 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1舱门正在上顶 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2舱门正在上顶 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load换盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1换盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2换盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto等待换盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>保存Auto1放料个数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>保存Auto2放料个数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>出料正在Auto1放料 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>出料正在Auto2放料 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1正在侧敲 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2正在侧敲 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix1Tray盘放置标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix1Tray盘拿走标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix2Tray盘放置标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix2Tray盘拿走标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix3Tray盘放置标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix3Tray盘拿走标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>总良率报警间隔计数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Socket使用次数超限数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>报警次数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>正在入料的Site = 99</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">trayTemp = </x:t>
-  </x:si>
-  <x:si>
-    <x:t>入料IC忽略 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>入料IC吸不起结批 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>无待测盘结批 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>出料IC忽略 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>测试IC忽略 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>载入数 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UphNumber = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1数量 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2数量 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix1数量 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix2数量 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fix3数量 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>空盘上顶到最大值 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>空盘下降到最小值 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1料仓满盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2料仓满盘标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1放盘等待标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2放盘等待标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty料仓打开标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load料仓打开标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1料仓打开标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2料仓打开标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>入料手臂工作完成标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>加热盘停止入料标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>入料手臂停止工作标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>测试手臂入料停止工作标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>测试手臂出料停止工作标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>出料手臂出料停止工作标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭停止工作 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>出料手臂工作完成标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>测试手臂工作完成标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>入料手臂抓料等待标记 = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭移动状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭前入料状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭前出料状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭后入料状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭后出料状态 = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty上顶标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load上顶标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1上顶标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2上顶标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty下降标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load下降标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Empty下降回零标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Load下降回零标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto1下降回零标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Auto2下降回零标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂取Empty空盘标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂取Load空盘标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂给Auto1空盘标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂给Auto2空盘标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂放空盘到Empty标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂放空盘到Auto1标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>抓盘手臂放空盘到Auto2标记 = 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InNozzleIC = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InNozzleICOpen = System.Boolean[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutNozzleIC = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutNozzleICOpen = System.Boolean[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TestNozzleIC = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TestNozzleICOpen = System.Boolean[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS初始化流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS初始化流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS结批流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS结批流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS入料手臂吸放料流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS入料手臂吸放料流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS出料手臂吸放料流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS出料手臂吸放料流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS入飞梭移动流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS入飞梭移动流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试手臂取待测料流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试手臂取待测料流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试手臂取已测料流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试手臂取已测料流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试区气缸下压动作流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试区气缸下压动作流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试区气缸上抬动作流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS测试区气缸上抬动作流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘上顶流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘上顶流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘下降流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘下降流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘下降回零流程.StepID = 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘下降回零流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS待测盘上顶流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS待测盘上顶流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS待测盘下降回零流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS待测盘下降回零流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘1上顶流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘1上顶流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘1下降回零流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘1下降回零流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘2上顶流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘2上顶流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘2下降回零流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS手动盘2下降回零流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂取Empty空盘流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂取Empty空盘流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂取Load空盘流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂取Load空盘流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Empty流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Empty流程.Processing = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Auto1流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Auto1流程.Processing =False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Auto2流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS抓盘手臂放空盘到Auto2流程.Processing=False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 15:25:00]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 15:28:33]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-02 15:41:57]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dout128PassNumber=0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dout128FailNumber=0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestState = 0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[0] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[0] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[0] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[0] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[0] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[0] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[1] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[1] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[1] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[1] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[1] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[1] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[2] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[2] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[2] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[2] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[2] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[2] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[3] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[3] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[3] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[3] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[3] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[3] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[4] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[4] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[4] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[4] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[4] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[4] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[5] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[5] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[5] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[5] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[5] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[5] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[6] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[6] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[6] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[6] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[6] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[6] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[7] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[7] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[7] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[7] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[7] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[7] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[8] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[8] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[8] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[8] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[8] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[8] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[9] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[9] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[9] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[9] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[9] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[9] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[10] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[10] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[10] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[10] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[10] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[10] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[11] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[11] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[11] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[11] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[11] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[11] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[12] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[12] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[12] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[12] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[12] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[12] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[13] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[13] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[13] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[13] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[13] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[13] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[14] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[14] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[14] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[14] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[14] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[14] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Com.Iswaitout[15] = False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestIC[15] = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>doutContinueFail[15] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良计数[15] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>单dut总不良累计计数[15] = 0,0,0,0,0,0,0,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SiteTestBin[15] = ,,,,,,,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BinSaveQueue=</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InSiteQueue=</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutSiteQueue=</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InNozzleICOpen = False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutNozzleICOpen = False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TestNozzleICOpen = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>正在吸取后入料 = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>正在放置前入料 = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭前入料IC = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭前出料IC = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭后入料IC = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>飞梭后出料IC = False,False,False,False,False,False,False,False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PS空盘下降回零流程.StepID = 500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-04 08:34:57]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 19:38:03]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 20:13:56]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 20:16:15]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 20:19:30]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 20:48:41]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 20:54:53]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 21:20:00]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-06 21:39:06]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-07 17:57:00]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-07 18:24:40]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-07 19:40:44]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 10:10:39]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400420,[Msg]归零失败!未初始化;未初始化;未初始化;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>归零失败</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 15:06:16]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 16:14:55]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 17:17:57]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 17:20:41]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 17:31:19]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 20:13:35]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-09 20:18:37]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-11 21:20:41]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[测试超时时间]:600-&gt;10:更新成功</x:t>
-  </x:si>
-  <x:si>
-    <x:t>@START_TEST 00 11111111+</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-11 21:29:21]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:16:55]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:22:35]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:34:51]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:36:16]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:39:48]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 09:41:01]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 11:22:59]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 11:26:26]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 11:30:43]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 11:33:47]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 11:35:21]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 14:00:47]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:10:26]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:12:27]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:14:06]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:15:53]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:23:19]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:25:31]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:27:38]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:28:40]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:29:43]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:30:54]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:32:16]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:40:52]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-12 16:52:58]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-13 10:51:18]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-13 11:30:47]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400449,[Msg]读取Site1-Site8探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400450,[Msg]读取Site9-Site16探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400451,[Msg]读取加热盘探测温度失败!详细信息:连接 192.168.1.5:502 失败，超时时间为 10000 ms</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-13 15:19:50]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-13 15:48:14]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-13 19:11:24]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10941,6 +9627,2372 @@
         <x:v>362</x:v>
       </x:c>
     </x:row>
+    <x:row r="662" spans="1:4">
+      <x:c r="A662" s="1">
+        <x:v>45883.3748022569</x:v>
+      </x:c>
+      <x:c r="B662" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C662" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D662" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" spans="1:4">
+      <x:c r="A663" s="1">
+        <x:v>45883.3748024884</x:v>
+      </x:c>
+      <x:c r="B663" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C663" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D663" s="2" t="s">
+        <x:v>366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" spans="1:4">
+      <x:c r="A664" s="1">
+        <x:v>45883.3749218866</x:v>
+      </x:c>
+      <x:c r="B664" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C664" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D664" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" spans="1:4">
+      <x:c r="A665" s="1">
+        <x:v>45883.3750378472</x:v>
+      </x:c>
+      <x:c r="B665" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C665" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D665" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" spans="1:4">
+      <x:c r="A666" s="1">
+        <x:v>45883.3751537384</x:v>
+      </x:c>
+      <x:c r="B666" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C666" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D666" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" spans="1:4">
+      <x:c r="A667" s="1">
+        <x:v>45883.3763067245</x:v>
+      </x:c>
+      <x:c r="B667" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C667" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D667" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" spans="1:4">
+      <x:c r="A668" s="1">
+        <x:v>45883.376307037</x:v>
+      </x:c>
+      <x:c r="B668" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C668" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D668" s="2" t="s">
+        <x:v>367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" spans="1:4">
+      <x:c r="A669" s="1">
+        <x:v>45883.3764338542</x:v>
+      </x:c>
+      <x:c r="B669" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C669" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D669" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" spans="1:4">
+      <x:c r="A670" s="1">
+        <x:v>45883.3765496296</x:v>
+      </x:c>
+      <x:c r="B670" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C670" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D670" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" spans="1:4">
+      <x:c r="A671" s="1">
+        <x:v>45883.3766654745</x:v>
+      </x:c>
+      <x:c r="B671" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C671" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D671" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" spans="1:4">
+      <x:c r="A672" s="1">
+        <x:v>45883.3772466551</x:v>
+      </x:c>
+      <x:c r="B672" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C672" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D672" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" spans="1:4">
+      <x:c r="A673" s="1">
+        <x:v>45883.3772468171</x:v>
+      </x:c>
+      <x:c r="B673" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C673" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D673" s="2" t="s">
+        <x:v>368</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" spans="1:4">
+      <x:c r="A674" s="1">
+        <x:v>45883.3773723264</x:v>
+      </x:c>
+      <x:c r="B674" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C674" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D674" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" spans="1:4">
+      <x:c r="A675" s="1">
+        <x:v>45883.3776565278</x:v>
+      </x:c>
+      <x:c r="B675" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C675" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D675" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" spans="1:4">
+      <x:c r="A676" s="1">
+        <x:v>45883.6638629977</x:v>
+      </x:c>
+      <x:c r="B676" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C676" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D676" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" spans="1:4">
+      <x:c r="A677" s="1">
+        <x:v>45883.6638631597</x:v>
+      </x:c>
+      <x:c r="B677" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C677" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D677" s="2" t="s">
+        <x:v>370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" spans="1:4">
+      <x:c r="A678" s="1">
+        <x:v>45883.6639948148</x:v>
+      </x:c>
+      <x:c r="B678" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C678" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D678" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" spans="1:4">
+      <x:c r="A679" s="1">
+        <x:v>45883.8059313773</x:v>
+      </x:c>
+      <x:c r="B679" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C679" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D679" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" spans="1:4">
+      <x:c r="A680" s="1">
+        <x:v>45883.8059315394</x:v>
+      </x:c>
+      <x:c r="B680" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C680" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D680" s="2" t="s">
+        <x:v>371</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" spans="1:4">
+      <x:c r="A681" s="1">
+        <x:v>45883.8060659259</x:v>
+      </x:c>
+      <x:c r="B681" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C681" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D681" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" spans="1:4">
+      <x:c r="A682" s="1">
+        <x:v>45883.8083585185</x:v>
+      </x:c>
+      <x:c r="B682" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C682" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D682" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" spans="1:4">
+      <x:c r="A683" s="1">
+        <x:v>45883.8083586806</x:v>
+      </x:c>
+      <x:c r="B683" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C683" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D683" s="2" t="s">
+        <x:v>372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" spans="1:4">
+      <x:c r="A684" s="1">
+        <x:v>45883.8084884259</x:v>
+      </x:c>
+      <x:c r="B684" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C684" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D684" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" spans="1:4">
+      <x:c r="A685" s="1">
+        <x:v>45883.9074601042</x:v>
+      </x:c>
+      <x:c r="B685" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C685" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D685" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" spans="1:4">
+      <x:c r="A686" s="1">
+        <x:v>45883.9074602778</x:v>
+      </x:c>
+      <x:c r="B686" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C686" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D686" s="2" t="s">
+        <x:v>373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" spans="1:4">
+      <x:c r="A687" s="1">
+        <x:v>45883.9075866088</x:v>
+      </x:c>
+      <x:c r="B687" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C687" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D687" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" spans="1:4">
+      <x:c r="A688" s="1">
+        <x:v>45884.4014456134</x:v>
+      </x:c>
+      <x:c r="B688" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C688" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D688" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" spans="1:4">
+      <x:c r="A689" s="1">
+        <x:v>45884.4014457755</x:v>
+      </x:c>
+      <x:c r="B689" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C689" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D689" s="2" t="s">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" spans="1:4">
+      <x:c r="A690" s="1">
+        <x:v>45884.4015704514</x:v>
+      </x:c>
+      <x:c r="B690" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C690" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D690" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" spans="1:4">
+      <x:c r="A691" s="1">
+        <x:v>45884.402473044</x:v>
+      </x:c>
+      <x:c r="B691" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C691" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D691" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" spans="1:4">
+      <x:c r="A692" s="1">
+        <x:v>45884.402473206</x:v>
+      </x:c>
+      <x:c r="B692" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C692" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D692" s="2" t="s">
+        <x:v>375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" spans="1:4">
+      <x:c r="A693" s="1">
+        <x:v>45884.4026027083</x:v>
+      </x:c>
+      <x:c r="B693" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C693" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D693" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" spans="1:4">
+      <x:c r="A694" s="1">
+        <x:v>45884.4251817361</x:v>
+      </x:c>
+      <x:c r="B694" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C694" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D694" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" spans="1:4">
+      <x:c r="A695" s="1">
+        <x:v>45884.425181875</x:v>
+      </x:c>
+      <x:c r="B695" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C695" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D695" s="2" t="s">
+        <x:v>376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" spans="1:4">
+      <x:c r="A696" s="1">
+        <x:v>45884.4253081944</x:v>
+      </x:c>
+      <x:c r="B696" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C696" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D696" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" spans="1:4">
+      <x:c r="A697" s="1">
+        <x:v>45884.8481649884</x:v>
+      </x:c>
+      <x:c r="B697" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C697" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D697" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" spans="1:4">
+      <x:c r="A698" s="1">
+        <x:v>45884.8481651505</x:v>
+      </x:c>
+      <x:c r="B698" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C698" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D698" s="2" t="s">
+        <x:v>377</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" spans="1:4">
+      <x:c r="A699" s="1">
+        <x:v>45884.8483000926</x:v>
+      </x:c>
+      <x:c r="B699" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C699" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D699" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" spans="1:4">
+      <x:c r="A700" s="1">
+        <x:v>45884.8783607986</x:v>
+      </x:c>
+      <x:c r="B700" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C700" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D700" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" spans="1:4">
+      <x:c r="A701" s="1">
+        <x:v>45884.8783610417</x:v>
+      </x:c>
+      <x:c r="B701" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C701" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D701" s="2" t="s">
+        <x:v>378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" spans="1:4">
+      <x:c r="A702" s="1">
+        <x:v>45884.8784795833</x:v>
+      </x:c>
+      <x:c r="B702" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C702" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D702" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" spans="1:4">
+      <x:c r="A703" s="1">
+        <x:v>45884.8950083912</x:v>
+      </x:c>
+      <x:c r="B703" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C703" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D703" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" spans="1:4">
+      <x:c r="A704" s="1">
+        <x:v>45884.8950086574</x:v>
+      </x:c>
+      <x:c r="B704" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C704" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D704" s="2" t="s">
+        <x:v>379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" spans="1:4">
+      <x:c r="A705" s="1">
+        <x:v>45885.6920727199</x:v>
+      </x:c>
+      <x:c r="B705" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C705" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D705" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" spans="1:4">
+      <x:c r="A706" s="1">
+        <x:v>45885.7073753356</x:v>
+      </x:c>
+      <x:c r="B706" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C706" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D706" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" spans="1:4">
+      <x:c r="A707" s="1">
+        <x:v>45885.7091754745</x:v>
+      </x:c>
+      <x:c r="B707" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C707" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D707" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" spans="1:4">
+      <x:c r="A708" s="1">
+        <x:v>45885.7169965162</x:v>
+      </x:c>
+      <x:c r="B708" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C708" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D708" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" spans="1:4">
+      <x:c r="A709" s="1">
+        <x:v>45885.7201106944</x:v>
+      </x:c>
+      <x:c r="B709" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C709" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D709" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" spans="1:4">
+      <x:c r="A710" s="1">
+        <x:v>45887.6920295602</x:v>
+      </x:c>
+      <x:c r="B710" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C710" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D710" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" spans="1:4">
+      <x:c r="A711" s="1">
+        <x:v>45888.668022037</x:v>
+      </x:c>
+      <x:c r="B711" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C711" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D711" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" spans="1:4">
+      <x:c r="A712" s="1">
+        <x:v>45888.6682709375</x:v>
+      </x:c>
+      <x:c r="B712" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C712" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D712" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" spans="1:4">
+      <x:c r="A713" s="1">
+        <x:v>45890.4354136806</x:v>
+      </x:c>
+      <x:c r="B713" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C713" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D713" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" spans="1:4">
+      <x:c r="A714" s="1">
+        <x:v>45890.4583522454</x:v>
+      </x:c>
+      <x:c r="B714" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C714" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D714" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" spans="1:4">
+      <x:c r="A715" s="1">
+        <x:v>45890.4588684954</x:v>
+      </x:c>
+      <x:c r="B715" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C715" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D715" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" spans="1:4">
+      <x:c r="A716" s="1">
+        <x:v>45890.4775973958</x:v>
+      </x:c>
+      <x:c r="B716" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C716" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D716" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" spans="1:4">
+      <x:c r="A717" s="1">
+        <x:v>45890.4776960995</x:v>
+      </x:c>
+      <x:c r="B717" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C717" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D717" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" spans="1:4">
+      <x:c r="A718" s="1">
+        <x:v>45890.4864343171</x:v>
+      </x:c>
+      <x:c r="B718" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C718" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D718" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" spans="1:4">
+      <x:c r="A719" s="1">
+        <x:v>45890.4864345139</x:v>
+      </x:c>
+      <x:c r="B719" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C719" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D719" s="2" t="s">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720" spans="1:4">
+      <x:c r="A720" s="1">
+        <x:v>45890.4865613542</x:v>
+      </x:c>
+      <x:c r="B720" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C720" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D720" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721" spans="1:4">
+      <x:c r="A721" s="1">
+        <x:v>45890.4992114236</x:v>
+      </x:c>
+      <x:c r="B721" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C721" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D721" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" spans="1:4">
+      <x:c r="A722" s="1">
+        <x:v>45890.4992116204</x:v>
+      </x:c>
+      <x:c r="B722" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C722" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D722" s="2" t="s">
+        <x:v>383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" spans="1:4">
+      <x:c r="A723" s="1">
+        <x:v>45890.4993511806</x:v>
+      </x:c>
+      <x:c r="B723" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C723" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D723" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" spans="1:4">
+      <x:c r="A724" s="1">
+        <x:v>45890.5750711458</x:v>
+      </x:c>
+      <x:c r="B724" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C724" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D724" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" spans="1:4">
+      <x:c r="A725" s="1">
+        <x:v>45890.5750713426</x:v>
+      </x:c>
+      <x:c r="B725" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C725" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D725" s="2" t="s">
+        <x:v>384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" spans="1:4">
+      <x:c r="A726" s="1">
+        <x:v>45890.579411713</x:v>
+      </x:c>
+      <x:c r="B726" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C726" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D726" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" spans="1:4">
+      <x:c r="A727" s="1">
+        <x:v>45890.5794117824</x:v>
+      </x:c>
+      <x:c r="B727" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C727" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D727" s="2" t="s">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" spans="1:4">
+      <x:c r="A728" s="1">
+        <x:v>45890.6049503009</x:v>
+      </x:c>
+      <x:c r="B728" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C728" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D728" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" spans="1:4">
+      <x:c r="A729" s="1">
+        <x:v>45890.6049505208</x:v>
+      </x:c>
+      <x:c r="B729" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C729" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D729" s="2" t="s">
+        <x:v>386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" spans="1:4">
+      <x:c r="A730" s="1">
+        <x:v>45890.6202611574</x:v>
+      </x:c>
+      <x:c r="B730" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C730" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D730" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" spans="1:4">
+      <x:c r="A731" s="1">
+        <x:v>45890.6202615393</x:v>
+      </x:c>
+      <x:c r="B731" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C731" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D731" s="2" t="s">
+        <x:v>387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732" spans="1:4">
+      <x:c r="A732" s="1">
+        <x:v>45890.6203884722</x:v>
+      </x:c>
+      <x:c r="B732" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C732" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D732" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="733" spans="1:4">
+      <x:c r="A733" s="1">
+        <x:v>45890.6638538079</x:v>
+      </x:c>
+      <x:c r="B733" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C733" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D733" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" spans="1:4">
+      <x:c r="A734" s="1">
+        <x:v>45890.6638540046</x:v>
+      </x:c>
+      <x:c r="B734" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C734" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D734" s="2" t="s">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735" spans="1:4">
+      <x:c r="A735" s="1">
+        <x:v>45890.663984213</x:v>
+      </x:c>
+      <x:c r="B735" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C735" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D735" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736" spans="1:4">
+      <x:c r="A736" s="1">
+        <x:v>45890.6740420833</x:v>
+      </x:c>
+      <x:c r="B736" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C736" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D736" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737" spans="1:4">
+      <x:c r="A737" s="1">
+        <x:v>45890.674042338</x:v>
+      </x:c>
+      <x:c r="B737" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C737" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D737" s="2" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738" spans="1:4">
+      <x:c r="A738" s="1">
+        <x:v>45890.674175787</x:v>
+      </x:c>
+      <x:c r="B738" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C738" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D738" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739" spans="1:4">
+      <x:c r="A739" s="1">
+        <x:v>45890.6752611343</x:v>
+      </x:c>
+      <x:c r="B739" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C739" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D739" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740" spans="1:4">
+      <x:c r="A740" s="1">
+        <x:v>45890.6752613194</x:v>
+      </x:c>
+      <x:c r="B740" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C740" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D740" s="2" t="s">
+        <x:v>390</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741" spans="1:4">
+      <x:c r="A741" s="1">
+        <x:v>45890.6793156944</x:v>
+      </x:c>
+      <x:c r="B741" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C741" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D741" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742" spans="1:4">
+      <x:c r="A742" s="1">
+        <x:v>45890.6793158796</x:v>
+      </x:c>
+      <x:c r="B742" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C742" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D742" s="2" t="s">
+        <x:v>391</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" spans="1:4">
+      <x:c r="A743" s="1">
+        <x:v>45890.6833212847</x:v>
+      </x:c>
+      <x:c r="B743" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C743" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D743" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" spans="1:4">
+      <x:c r="A744" s="1">
+        <x:v>45890.6833214931</x:v>
+      </x:c>
+      <x:c r="B744" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C744" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D744" s="2" t="s">
+        <x:v>392</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" spans="1:4">
+      <x:c r="A745" s="1">
+        <x:v>45890.6869888542</x:v>
+      </x:c>
+      <x:c r="B745" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C745" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D745" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" spans="1:4">
+      <x:c r="A746" s="1">
+        <x:v>45890.6869890394</x:v>
+      </x:c>
+      <x:c r="B746" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C746" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D746" s="2" t="s">
+        <x:v>393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747" spans="1:4">
+      <x:c r="A747" s="1">
+        <x:v>45890.6871198958</x:v>
+      </x:c>
+      <x:c r="B747" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C747" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D747" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748" spans="1:4">
+      <x:c r="A748" s="1">
+        <x:v>45890.6875063194</x:v>
+      </x:c>
+      <x:c r="B748" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C748" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D748" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749" spans="1:4">
+      <x:c r="A749" s="1">
+        <x:v>45890.6894295602</x:v>
+      </x:c>
+      <x:c r="B749" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C749" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D749" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750" spans="1:4">
+      <x:c r="A750" s="1">
+        <x:v>45890.6894297685</x:v>
+      </x:c>
+      <x:c r="B750" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C750" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D750" s="2" t="s">
+        <x:v>394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751" spans="1:4">
+      <x:c r="A751" s="1">
+        <x:v>45890.6895591551</x:v>
+      </x:c>
+      <x:c r="B751" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C751" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D751" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752" spans="1:4">
+      <x:c r="A752" s="1">
+        <x:v>45890.6907923495</x:v>
+      </x:c>
+      <x:c r="B752" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C752" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D752" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753" spans="1:4">
+      <x:c r="A753" s="1">
+        <x:v>45890.6907925694</x:v>
+      </x:c>
+      <x:c r="B753" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C753" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D753" s="2" t="s">
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754" spans="1:4">
+      <x:c r="A754" s="1">
+        <x:v>45890.691101412</x:v>
+      </x:c>
+      <x:c r="B754" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C754" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D754" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" spans="1:4">
+      <x:c r="A755" s="1">
+        <x:v>45890.6936439931</x:v>
+      </x:c>
+      <x:c r="B755" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C755" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D755" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" spans="1:4">
+      <x:c r="A756" s="1">
+        <x:v>45890.6936441782</x:v>
+      </x:c>
+      <x:c r="B756" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C756" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D756" s="2" t="s">
+        <x:v>396</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" spans="1:4">
+      <x:c r="A757" s="1">
+        <x:v>45890.6937734722</x:v>
+      </x:c>
+      <x:c r="B757" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C757" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D757" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" spans="1:4">
+      <x:c r="A758" s="1">
+        <x:v>45890.6970851505</x:v>
+      </x:c>
+      <x:c r="B758" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C758" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D758" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" spans="1:4">
+      <x:c r="A759" s="1">
+        <x:v>45890.6970854745</x:v>
+      </x:c>
+      <x:c r="B759" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C759" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D759" s="2" t="s">
+        <x:v>397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" spans="1:4">
+      <x:c r="A760" s="1">
+        <x:v>45890.699049919</x:v>
+      </x:c>
+      <x:c r="B760" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C760" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D760" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" spans="1:4">
+      <x:c r="A761" s="1">
+        <x:v>45890.6990501157</x:v>
+      </x:c>
+      <x:c r="B761" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C761" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D761" s="2" t="s">
+        <x:v>398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" spans="1:4">
+      <x:c r="A762" s="1">
+        <x:v>45890.6992210648</x:v>
+      </x:c>
+      <x:c r="B762" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C762" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D762" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" spans="1:4">
+      <x:c r="A763" s="1">
+        <x:v>45890.7001345949</x:v>
+      </x:c>
+      <x:c r="B763" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C763" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D763" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" spans="1:4">
+      <x:c r="A764" s="1">
+        <x:v>45890.7001346412</x:v>
+      </x:c>
+      <x:c r="B764" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C764" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D764" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" spans="1:4">
+      <x:c r="A765" s="1">
+        <x:v>45890.7349170718</x:v>
+      </x:c>
+      <x:c r="B765" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C765" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D765" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" spans="1:4">
+      <x:c r="A766" s="1">
+        <x:v>45890.7349172569</x:v>
+      </x:c>
+      <x:c r="B766" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C766" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D766" s="2" t="s">
+        <x:v>401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" spans="1:4">
+      <x:c r="A767" s="1">
+        <x:v>45890.8046995023</x:v>
+      </x:c>
+      <x:c r="B767" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C767" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D767" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" spans="1:4">
+      <x:c r="A768" s="1">
+        <x:v>45890.8046996875</x:v>
+      </x:c>
+      <x:c r="B768" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C768" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D768" s="2" t="s">
+        <x:v>402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" spans="1:4">
+      <x:c r="A769" s="1">
+        <x:v>45890.8069965162</x:v>
+      </x:c>
+      <x:c r="B769" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C769" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D769" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" spans="1:4">
+      <x:c r="A770" s="1">
+        <x:v>45890.8069968634</x:v>
+      </x:c>
+      <x:c r="B770" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C770" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D770" s="2" t="s">
+        <x:v>403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" spans="1:4">
+      <x:c r="A771" s="1">
+        <x:v>45890.8071871759</x:v>
+      </x:c>
+      <x:c r="B771" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C771" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D771" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" spans="1:4">
+      <x:c r="A772" s="1">
+        <x:v>45890.8114173727</x:v>
+      </x:c>
+      <x:c r="B772" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C772" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D772" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" spans="1:4">
+      <x:c r="A773" s="1">
+        <x:v>45890.8114177431</x:v>
+      </x:c>
+      <x:c r="B773" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C773" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D773" s="2" t="s">
+        <x:v>404</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" spans="1:4">
+      <x:c r="A774" s="1">
+        <x:v>45890.8114594907</x:v>
+      </x:c>
+      <x:c r="B774" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C774" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D774" s="2" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" spans="1:4">
+      <x:c r="A775" s="1">
+        <x:v>45890.8115451736</x:v>
+      </x:c>
+      <x:c r="B775" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C775" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D775" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" spans="1:4">
+      <x:c r="A776" s="1">
+        <x:v>45890.817050625</x:v>
+      </x:c>
+      <x:c r="B776" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C776" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D776" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" spans="1:4">
+      <x:c r="A777" s="1">
+        <x:v>45890.8170508102</x:v>
+      </x:c>
+      <x:c r="B777" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C777" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D777" s="2" t="s">
+        <x:v>406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" spans="1:4">
+      <x:c r="A778" s="1">
+        <x:v>45890.8171284954</x:v>
+      </x:c>
+      <x:c r="B778" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C778" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D778" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" spans="1:4">
+      <x:c r="A779" s="1">
+        <x:v>45890.8171795833</x:v>
+      </x:c>
+      <x:c r="B779" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C779" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D779" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" spans="1:4">
+      <x:c r="A780" s="1">
+        <x:v>45890.8180695486</x:v>
+      </x:c>
+      <x:c r="B780" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C780" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D780" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" spans="1:4">
+      <x:c r="A781" s="1">
+        <x:v>45890.8184985764</x:v>
+      </x:c>
+      <x:c r="B781" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C781" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D781" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" spans="1:4">
+      <x:c r="A782" s="1">
+        <x:v>45890.8185776042</x:v>
+      </x:c>
+      <x:c r="B782" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C782" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D782" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" spans="1:4">
+      <x:c r="A783" s="1">
+        <x:v>45890.8187643866</x:v>
+      </x:c>
+      <x:c r="B783" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C783" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D783" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" spans="1:4">
+      <x:c r="A784" s="1">
+        <x:v>45890.8188492477</x:v>
+      </x:c>
+      <x:c r="B784" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C784" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D784" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" spans="1:4">
+      <x:c r="A785" s="1">
+        <x:v>45890.8192801042</x:v>
+      </x:c>
+      <x:c r="B785" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C785" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D785" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" spans="1:4">
+      <x:c r="A786" s="1">
+        <x:v>45890.8192804398</x:v>
+      </x:c>
+      <x:c r="B786" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C786" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D786" s="2" t="s">
+        <x:v>408</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" spans="1:4">
+      <x:c r="A787" s="1">
+        <x:v>45890.8194959491</x:v>
+      </x:c>
+      <x:c r="B787" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C787" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D787" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" spans="1:4">
+      <x:c r="A788" s="1">
+        <x:v>45890.820320162</x:v>
+      </x:c>
+      <x:c r="B788" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C788" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D788" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" spans="1:4">
+      <x:c r="A789" s="1">
+        <x:v>45890.8212386458</x:v>
+      </x:c>
+      <x:c r="B789" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C789" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D789" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" spans="1:4">
+      <x:c r="A790" s="1">
+        <x:v>45890.8212387037</x:v>
+      </x:c>
+      <x:c r="B790" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C790" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D790" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" spans="1:4">
+      <x:c r="A791" s="1">
+        <x:v>45890.8223301736</x:v>
+      </x:c>
+      <x:c r="B791" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C791" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D791" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" spans="1:4">
+      <x:c r="A792" s="1">
+        <x:v>45890.8223303704</x:v>
+      </x:c>
+      <x:c r="B792" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C792" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D792" s="2" t="s">
+        <x:v>409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" spans="1:4">
+      <x:c r="A793" s="1">
+        <x:v>45890.8224690857</x:v>
+      </x:c>
+      <x:c r="B793" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C793" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D793" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" spans="1:4">
+      <x:c r="A794" s="1">
+        <x:v>45890.8230941667</x:v>
+      </x:c>
+      <x:c r="B794" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C794" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D794" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" spans="1:4">
+      <x:c r="A795" s="1">
+        <x:v>45890.823094375</x:v>
+      </x:c>
+      <x:c r="B795" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C795" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D795" s="2" t="s">
+        <x:v>410</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" spans="1:4">
+      <x:c r="A796" s="1">
+        <x:v>45890.8232665856</x:v>
+      </x:c>
+      <x:c r="B796" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C796" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D796" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" spans="1:4">
+      <x:c r="A797" s="1">
+        <x:v>45890.8246544329</x:v>
+      </x:c>
+      <x:c r="B797" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C797" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D797" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" spans="1:4">
+      <x:c r="A798" s="1">
+        <x:v>45890.8246546296</x:v>
+      </x:c>
+      <x:c r="B798" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C798" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D798" s="2" t="s">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" spans="1:4">
+      <x:c r="A799" s="1">
+        <x:v>45890.8268080324</x:v>
+      </x:c>
+      <x:c r="B799" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C799" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D799" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" spans="1:4">
+      <x:c r="A800" s="1">
+        <x:v>45890.8268082292</x:v>
+      </x:c>
+      <x:c r="B800" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C800" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D800" s="2" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" spans="1:4">
+      <x:c r="A801" s="1">
+        <x:v>45890.8387857755</x:v>
+      </x:c>
+      <x:c r="B801" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C801" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D801" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" spans="1:4">
+      <x:c r="A802" s="1">
+        <x:v>45890.8387859606</x:v>
+      </x:c>
+      <x:c r="B802" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C802" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D802" s="2" t="s">
+        <x:v>413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" spans="1:4">
+      <x:c r="A803" s="1">
+        <x:v>45890.8389151736</x:v>
+      </x:c>
+      <x:c r="B803" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C803" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D803" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" spans="1:4">
+      <x:c r="A804" s="1">
+        <x:v>45890.8406661343</x:v>
+      </x:c>
+      <x:c r="B804" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C804" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D804" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" spans="1:4">
+      <x:c r="A805" s="1">
+        <x:v>45890.8406663194</x:v>
+      </x:c>
+      <x:c r="B805" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C805" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D805" s="2" t="s">
+        <x:v>414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" spans="1:4">
+      <x:c r="A806" s="1">
+        <x:v>45890.8408404282</x:v>
+      </x:c>
+      <x:c r="B806" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C806" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D806" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" spans="1:4">
+      <x:c r="A807" s="1">
+        <x:v>45890.8433281019</x:v>
+      </x:c>
+      <x:c r="B807" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C807" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D807" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" spans="1:4">
+      <x:c r="A808" s="1">
+        <x:v>45890.8433284375</x:v>
+      </x:c>
+      <x:c r="B808" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C808" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D808" s="2" t="s">
+        <x:v>415</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" spans="1:4">
+      <x:c r="A809" s="1">
+        <x:v>45890.8434571875</x:v>
+      </x:c>
+      <x:c r="B809" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C809" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D809" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" spans="1:4">
+      <x:c r="A810" s="1">
+        <x:v>45890.8448894213</x:v>
+      </x:c>
+      <x:c r="B810" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C810" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D810" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" spans="1:4">
+      <x:c r="A811" s="1">
+        <x:v>45890.8448897454</x:v>
+      </x:c>
+      <x:c r="B811" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C811" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D811" s="2" t="s">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" spans="1:4">
+      <x:c r="A812" s="1">
+        <x:v>45890.8450194676</x:v>
+      </x:c>
+      <x:c r="B812" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C812" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D812" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" spans="1:4">
+      <x:c r="A813" s="1">
+        <x:v>45890.8466671296</x:v>
+      </x:c>
+      <x:c r="B813" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C813" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D813" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" spans="1:4">
+      <x:c r="A814" s="1">
+        <x:v>45890.846667338</x:v>
+      </x:c>
+      <x:c r="B814" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C814" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D814" s="2" t="s">
+        <x:v>417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" spans="1:4">
+      <x:c r="A815" s="1">
+        <x:v>45890.8467891782</x:v>
+      </x:c>
+      <x:c r="B815" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C815" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D815" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" spans="1:4">
+      <x:c r="A816" s="1">
+        <x:v>45890.8489122106</x:v>
+      </x:c>
+      <x:c r="B816" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C816" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D816" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" spans="1:4">
+      <x:c r="A817" s="1">
+        <x:v>45890.8489123958</x:v>
+      </x:c>
+      <x:c r="B817" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C817" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D817" s="2" t="s">
+        <x:v>418</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" spans="1:4">
+      <x:c r="A818" s="1">
+        <x:v>45890.8490851042</x:v>
+      </x:c>
+      <x:c r="B818" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C818" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D818" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" spans="1:4">
+      <x:c r="A819" s="1">
+        <x:v>45890.8521935648</x:v>
+      </x:c>
+      <x:c r="B819" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C819" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D819" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" spans="1:4">
+      <x:c r="A820" s="1">
+        <x:v>45890.85219375</x:v>
+      </x:c>
+      <x:c r="B820" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C820" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D820" s="2" t="s">
+        <x:v>419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" spans="1:4">
+      <x:c r="A821" s="1">
+        <x:v>45890.8523198495</x:v>
+      </x:c>
+      <x:c r="B821" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C821" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D821" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822" spans="1:4">
+      <x:c r="A822" s="1">
+        <x:v>45890.8540117593</x:v>
+      </x:c>
+      <x:c r="B822" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C822" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D822" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823" spans="1:4">
+      <x:c r="A823" s="1">
+        <x:v>45890.8540119444</x:v>
+      </x:c>
+      <x:c r="B823" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C823" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D823" s="2" t="s">
+        <x:v>420</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824" spans="1:4">
+      <x:c r="A824" s="1">
+        <x:v>45890.8540696065</x:v>
+      </x:c>
+      <x:c r="B824" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C824" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D824" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825" spans="1:4">
+      <x:c r="A825" s="1">
+        <x:v>45890.8541827662</x:v>
+      </x:c>
+      <x:c r="B825" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C825" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D825" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826" spans="1:4">
+      <x:c r="A826" s="1">
+        <x:v>45890.8550311458</x:v>
+      </x:c>
+      <x:c r="B826" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C826" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D826" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827" spans="1:4">
+      <x:c r="A827" s="1">
+        <x:v>45890.855031331</x:v>
+      </x:c>
+      <x:c r="B827" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C827" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D827" s="2" t="s">
+        <x:v>421</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828" spans="1:4">
+      <x:c r="A828" s="1">
+        <x:v>45890.8551766782</x:v>
+      </x:c>
+      <x:c r="B828" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C828" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D828" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829" spans="1:4">
+      <x:c r="A829" s="1">
+        <x:v>45890.8559021875</x:v>
+      </x:c>
+      <x:c r="B829" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C829" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D829" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830" spans="1:4">
+      <x:c r="A830" s="1">
+        <x:v>45890.8559024306</x:v>
+      </x:c>
+      <x:c r="B830" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C830" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D830" s="2" t="s">
+        <x:v>422</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
